--- a/ssp_modeling/scenario_mapping/ssp_uganda_transformation_cw_NDC_2.0.xlsx
+++ b/ssp_modeling/scenario_mapping/ssp_uganda_transformation_cw_NDC_2.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_uganda_data/ssp_modeling/scenario_mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1345131C-46B7-D147-98C1-642C5E93D0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A54F316-91D1-244B-8C5B-64FEA5AAEAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="-7260" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-720" windowWidth="38000" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -3942,7 +3942,9 @@
       <c r="N35" s="11">
         <v>1</v>
       </c>
-      <c r="O35" s="11"/>
+      <c r="O35" s="53">
+        <v>0.5</v>
+      </c>
       <c r="P35" s="11">
         <v>1</v>
       </c>
@@ -3984,7 +3986,7 @@
       <c r="N36" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="O36" s="11"/>
+      <c r="O36" s="53"/>
       <c r="P36" s="11">
         <v>1</v>
       </c>
@@ -4024,7 +4026,9 @@
       <c r="N37" s="11">
         <v>1</v>
       </c>
-      <c r="O37" s="11"/>
+      <c r="O37" s="53">
+        <v>0.5</v>
+      </c>
       <c r="P37" s="11">
         <v>1</v>
       </c>
@@ -4218,7 +4222,9 @@
       <c r="P41" s="11">
         <v>2</v>
       </c>
-      <c r="Q41" s="53"/>
+      <c r="Q41" s="53">
+        <v>1</v>
+      </c>
       <c r="R41" s="11"/>
     </row>
     <row r="42" spans="1:18" ht="85" x14ac:dyDescent="0.2">
@@ -4352,9 +4358,7 @@
       <c r="P44" s="11">
         <v>1</v>
       </c>
-      <c r="Q44" s="53">
-        <v>1</v>
-      </c>
+      <c r="Q44" s="53"/>
       <c r="R44" s="11"/>
     </row>
     <row r="45" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -4406,7 +4410,9 @@
       <c r="P45" s="11">
         <v>2</v>
       </c>
-      <c r="Q45" s="53"/>
+      <c r="Q45" s="53">
+        <v>1</v>
+      </c>
       <c r="R45" s="11"/>
     </row>
     <row r="46" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -4802,10 +4808,10 @@
         <v>0.5</v>
       </c>
       <c r="P53" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q53" s="53">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="Q53" s="11">
+        <v>0.5</v>
       </c>
       <c r="R53" s="11"/>
     </row>
@@ -4856,10 +4862,10 @@
         <v>0.5</v>
       </c>
       <c r="P54" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q54" s="53">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="Q54" s="11">
+        <v>0.5</v>
       </c>
       <c r="R54" s="11"/>
     </row>
@@ -4910,10 +4916,10 @@
         <v>0.5</v>
       </c>
       <c r="P55" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q55" s="53">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="Q55" s="11">
+        <v>0.5</v>
       </c>
       <c r="R55" s="11"/>
     </row>
@@ -4964,9 +4970,9 @@
         <v>1</v>
       </c>
       <c r="P56" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q56" s="53">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="11">
         <v>1</v>
       </c>
       <c r="R56" s="11"/>
@@ -5009,12 +5015,8 @@
         <v>1</v>
       </c>
       <c r="O57" s="11"/>
-      <c r="P57" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q57" s="53">
-        <v>1</v>
-      </c>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="11"/>
       <c r="R57" s="11"/>
     </row>
     <row r="58" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -5062,9 +5064,9 @@
         <v>1</v>
       </c>
       <c r="P58" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q58" s="53">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="11">
         <v>1</v>
       </c>
       <c r="R58" s="11"/>
@@ -5107,10 +5109,8 @@
         <v>1</v>
       </c>
       <c r="O59" s="11"/>
-      <c r="P59" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q59" s="53"/>
+      <c r="P59" s="11"/>
+      <c r="Q59" s="11"/>
       <c r="R59" s="11"/>
     </row>
     <row r="60" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -5151,10 +5151,8 @@
         <v>1</v>
       </c>
       <c r="O60" s="11"/>
-      <c r="P60" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q60" s="53"/>
+      <c r="P60" s="11"/>
+      <c r="Q60" s="11"/>
       <c r="R60" s="11"/>
     </row>
     <row r="61" spans="1:18" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -5204,10 +5202,10 @@
         <v>0.5</v>
       </c>
       <c r="P61" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q61" s="53">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="Q61" s="11">
+        <v>0.5</v>
       </c>
       <c r="R61" s="11"/>
     </row>
@@ -5258,10 +5256,10 @@
         <v>0.5</v>
       </c>
       <c r="P62" s="11">
-        <v>1</v>
-      </c>
-      <c r="Q62" s="53">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="Q62" s="11">
+        <v>0.5</v>
       </c>
       <c r="R62" s="11"/>
     </row>
@@ -5283,7 +5281,7 @@
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="I1:L1">
-    <cfRule type="colorScale" priority="97">
+    <cfRule type="colorScale" priority="102">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5295,7 +5293,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2">
-    <cfRule type="colorScale" priority="87">
+    <cfRule type="colorScale" priority="92">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5305,7 +5303,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="88">
+    <cfRule type="colorScale" priority="93">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5317,7 +5315,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J24">
-    <cfRule type="colorScale" priority="169">
+    <cfRule type="colorScale" priority="173">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5327,7 +5325,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="168">
+    <cfRule type="colorScale" priority="174">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5339,7 +5337,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:N1048576">
-    <cfRule type="colorScale" priority="76">
+    <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5351,7 +5349,203 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2">
-    <cfRule type="colorScale" priority="77">
+    <cfRule type="colorScale" priority="82">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N22:R22">
+    <cfRule type="colorScale" priority="183">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O3:O4 O11:O12 O15 O19:O21 O43:O44 O47 O51 O26:O34 O32:P32 R32 O57:Q57 O38:O39">
+    <cfRule type="colorScale" priority="75">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O7">
+    <cfRule type="colorScale" priority="67">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O8:O34 O32:P32 R32 O1:O6 O38:O1048576">
+    <cfRule type="colorScale" priority="80">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O22">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O26:O32 O32:P32 R32">
+    <cfRule type="colorScale" priority="72">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="69">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O38">
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="62">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O39">
+    <cfRule type="colorScale" priority="61">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O43:O44 O51 O47 O19:O21 O11:O12 O15 O3:O4 O7 O26:O34 O32:P32 R32 O57:Q57 O38:O39">
+    <cfRule type="colorScale" priority="68">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O23:P25 P30:P31 N23:N62 N8:P21 O26:O32 R32 N2:P6 O32:P34 O38:P62 P35:P37">
+    <cfRule type="colorScale" priority="178">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O32:P32 R32">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O22:R22">
+    <cfRule type="colorScale" priority="184">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P1:P1048576 O2:P6">
+    <cfRule type="colorScale" priority="79">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5363,203 +5557,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N7 P7 R7">
-    <cfRule type="colorScale" priority="186">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N22:R22">
-    <cfRule type="colorScale" priority="178">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O3:O4 O11:O12 O15 O19:O21 O43:O44 O47 O51 O57 O26:O39 O32:P32 R32">
-    <cfRule type="colorScale" priority="70">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O7">
-    <cfRule type="colorScale" priority="62">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O8:O1048576 O32:P32 R32 O1:O6">
-    <cfRule type="colorScale" priority="75">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O22">
-    <cfRule type="colorScale" priority="53">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O26:O32 O32:P32 R32">
-    <cfRule type="colorScale" priority="67">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O38">
-    <cfRule type="colorScale" priority="57">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="58">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O39">
-    <cfRule type="colorScale" priority="55">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O43:O44 O57 O51 O47 O19:O21 O11:O12 O15 O3:O4 O7 O26:O39 O32:P32 R32">
-    <cfRule type="colorScale" priority="63">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P1:P1048576 O2:P6">
-    <cfRule type="colorScale" priority="74">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O23:P25 P30:P31 N23:N62 N8:P21 O26:O32 O32:P62 R32 N2:P6">
-    <cfRule type="colorScale" priority="173">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O32:P32 R32">
-    <cfRule type="colorScale" priority="31">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="30">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O22:R22">
-    <cfRule type="colorScale" priority="179">
+    <cfRule type="colorScale" priority="191">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5571,7 +5569,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:P10">
-    <cfRule type="colorScale" priority="61">
+    <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5582,8 +5580,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P26 R26">
-    <cfRule type="colorScale" priority="188">
+  <conditionalFormatting sqref="P26:P31 P7 O8:P25 R1:R1048576 O1:P6 O32:P34 O38:P1048576 P35:P37">
+    <cfRule type="colorScale" priority="185">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5594,8 +5592,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P26:P31 P7 O8:P25 O32:P1048576 R1:R1048576 O1:P6">
-    <cfRule type="colorScale" priority="180">
+  <conditionalFormatting sqref="P53:P62">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5606,8 +5604,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P27 R27">
-    <cfRule type="colorScale" priority="189">
+  <conditionalFormatting sqref="Q2">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5617,45 +5615,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P28 R28">
-    <cfRule type="colorScale" priority="190">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P29 R29">
-    <cfRule type="colorScale" priority="191">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q23:Q1048576 Q1 Q5:Q21">
     <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q22">
-    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5686,8 +5646,168 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q3">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q22">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q23:Q52 Q1 Q5:Q21 Q63:Q1048576">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q53:Q62">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R1:R1048576">
-    <cfRule type="colorScale" priority="192">
+    <cfRule type="colorScale" priority="197">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5699,6 +5819,30 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R8:R10">
+    <cfRule type="colorScale" priority="198">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R23:R25 R8:R21 R30:R62 R2:R6">
+    <cfRule type="colorScale" priority="199">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P26 R26">
     <cfRule type="colorScale" priority="193">
       <colorScale>
         <cfvo type="min"/>
@@ -5710,7 +5854,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R23:R25 R8:R21 R30:R62 R2:R6">
+  <conditionalFormatting sqref="P27 R27">
     <cfRule type="colorScale" priority="194">
       <colorScale>
         <cfvo type="min"/>
@@ -5722,7 +5866,81 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P28 R28">
+    <cfRule type="colorScale" priority="195">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P29 R29">
+    <cfRule type="colorScale" priority="196">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="U32">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
@@ -5783,191 +6001,9 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q3">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q3">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q3">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q3">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4">
+  <conditionalFormatting sqref="O35:O37">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4">
-    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7030,9 +7066,9 @@
       <c r="D35" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="E35" s="35" t="str">
+      <c r="E35" s="35">
         <f>+IF(VLOOKUP($B35,main!$C$2:$R$62,13,FALSE)=0,"",VLOOKUP($B35,main!$C$2:$R$62,13,FALSE))</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="F35" s="35">
         <f>+IF(VLOOKUP($B35,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B35,main!$C$2:$R$62,14,FALSE))</f>
@@ -7090,9 +7126,9 @@
       <c r="D37" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="E37" s="35" t="str">
+      <c r="E37" s="35">
         <f>+IF(VLOOKUP($B37,main!$C$2:$R$62,13,FALSE)=0,"",VLOOKUP($B37,main!$C$2:$R$62,13,FALSE))</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="F37" s="35">
         <f>+IF(VLOOKUP($B37,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B37,main!$C$2:$R$62,14,FALSE))</f>
@@ -7218,9 +7254,9 @@
         <f>+IF(VLOOKUP($B41,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B41,main!$C$2:$R$62,14,FALSE))</f>
         <v>2</v>
       </c>
-      <c r="G41" s="35" t="str">
+      <c r="G41" s="35">
         <f>+IF(VLOOKUP($B41,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B41,main!$C$2:$R$62,15,FALSE))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H41" s="35" t="str">
         <f>+IF(VLOOKUP($B41,main!$C$2:$R$62,16,FALSE)=0,"",VLOOKUP($B41,main!$C$2:$R$62,16,FALSE))</f>
@@ -7308,9 +7344,9 @@
         <f>+IF(VLOOKUP($B44,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B44,main!$C$2:$R$62,14,FALSE))</f>
         <v>1</v>
       </c>
-      <c r="G44" s="35">
+      <c r="G44" s="35" t="str">
         <f>+IF(VLOOKUP($B44,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B44,main!$C$2:$R$62,15,FALSE))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="H44" s="35" t="str">
         <f>+IF(VLOOKUP($B44,main!$C$2:$R$62,16,FALSE)=0,"",VLOOKUP($B44,main!$C$2:$R$62,16,FALSE))</f>
@@ -7338,9 +7374,9 @@
         <f>+IF(VLOOKUP($B45,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B45,main!$C$2:$R$62,14,FALSE))</f>
         <v>2</v>
       </c>
-      <c r="G45" s="35" t="str">
+      <c r="G45" s="35">
         <f>+IF(VLOOKUP($B45,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B45,main!$C$2:$R$62,15,FALSE))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H45" s="35" t="str">
         <f>+IF(VLOOKUP($B45,main!$C$2:$R$62,16,FALSE)=0,"",VLOOKUP($B45,main!$C$2:$R$62,16,FALSE))</f>
@@ -7576,11 +7612,11 @@
       </c>
       <c r="F53" s="35">
         <f>+IF(VLOOKUP($B53,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B53,main!$C$2:$R$62,14,FALSE))</f>
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G53" s="35">
         <f>+IF(VLOOKUP($B53,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B53,main!$C$2:$R$62,15,FALSE))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H53" s="35" t="str">
         <f>+IF(VLOOKUP($B53,main!$C$2:$R$62,16,FALSE)=0,"",VLOOKUP($B53,main!$C$2:$R$62,16,FALSE))</f>
@@ -7606,11 +7642,11 @@
       </c>
       <c r="F54" s="35">
         <f>+IF(VLOOKUP($B54,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B54,main!$C$2:$R$62,14,FALSE))</f>
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G54" s="35">
         <f>+IF(VLOOKUP($B54,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B54,main!$C$2:$R$62,15,FALSE))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H54" s="35" t="str">
         <f>+IF(VLOOKUP($B54,main!$C$2:$R$62,16,FALSE)=0,"",VLOOKUP($B54,main!$C$2:$R$62,16,FALSE))</f>
@@ -7636,11 +7672,11 @@
       </c>
       <c r="F55" s="35">
         <f>+IF(VLOOKUP($B55,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B55,main!$C$2:$R$62,14,FALSE))</f>
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G55" s="35">
         <f>+IF(VLOOKUP($B55,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B55,main!$C$2:$R$62,15,FALSE))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H55" s="35" t="str">
         <f>+IF(VLOOKUP($B55,main!$C$2:$R$62,16,FALSE)=0,"",VLOOKUP($B55,main!$C$2:$R$62,16,FALSE))</f>
@@ -7666,7 +7702,7 @@
       </c>
       <c r="F56" s="35">
         <f>+IF(VLOOKUP($B56,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B56,main!$C$2:$R$62,14,FALSE))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56" s="35">
         <f>+IF(VLOOKUP($B56,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B56,main!$C$2:$R$62,15,FALSE))</f>
@@ -7694,13 +7730,13 @@
         <f>+IF(VLOOKUP($B57,main!$C$2:$R$62,13,FALSE)=0,"",VLOOKUP($B57,main!$C$2:$R$62,13,FALSE))</f>
         <v/>
       </c>
-      <c r="F57" s="35">
+      <c r="F57" s="35" t="str">
         <f>+IF(VLOOKUP($B57,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B57,main!$C$2:$R$62,14,FALSE))</f>
-        <v>1</v>
-      </c>
-      <c r="G57" s="35">
+        <v/>
+      </c>
+      <c r="G57" s="35" t="str">
         <f>+IF(VLOOKUP($B57,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B57,main!$C$2:$R$62,15,FALSE))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="H57" s="35" t="str">
         <f>+IF(VLOOKUP($B57,main!$C$2:$R$62,16,FALSE)=0,"",VLOOKUP($B57,main!$C$2:$R$62,16,FALSE))</f>
@@ -7726,7 +7762,7 @@
       </c>
       <c r="F58" s="35">
         <f>+IF(VLOOKUP($B58,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B58,main!$C$2:$R$62,14,FALSE))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="35">
         <f>+IF(VLOOKUP($B58,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B58,main!$C$2:$R$62,15,FALSE))</f>
@@ -7754,9 +7790,9 @@
         <f>+IF(VLOOKUP($B59,main!$C$2:$R$62,13,FALSE)=0,"",VLOOKUP($B59,main!$C$2:$R$62,13,FALSE))</f>
         <v/>
       </c>
-      <c r="F59" s="35">
+      <c r="F59" s="35" t="str">
         <f>+IF(VLOOKUP($B59,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B59,main!$C$2:$R$62,14,FALSE))</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="G59" s="35" t="str">
         <f>+IF(VLOOKUP($B59,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B59,main!$C$2:$R$62,15,FALSE))</f>
@@ -7784,9 +7820,9 @@
         <f>+IF(VLOOKUP($B60,main!$C$2:$R$62,13,FALSE)=0,"",VLOOKUP($B60,main!$C$2:$R$62,13,FALSE))</f>
         <v/>
       </c>
-      <c r="F60" s="35">
+      <c r="F60" s="35" t="str">
         <f>+IF(VLOOKUP($B60,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B60,main!$C$2:$R$62,14,FALSE))</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="G60" s="35" t="str">
         <f>+IF(VLOOKUP($B60,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B60,main!$C$2:$R$62,15,FALSE))</f>
@@ -7816,11 +7852,11 @@
       </c>
       <c r="F61" s="35">
         <f>+IF(VLOOKUP($B61,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B61,main!$C$2:$R$62,14,FALSE))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G61" s="35">
         <f>+IF(VLOOKUP($B61,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B61,main!$C$2:$R$62,15,FALSE))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H61" s="35" t="str">
         <f>+IF(VLOOKUP($B61,main!$C$2:$R$62,16,FALSE)=0,"",VLOOKUP($B61,main!$C$2:$R$62,16,FALSE))</f>
@@ -7846,11 +7882,11 @@
       </c>
       <c r="F62" s="35">
         <f>+IF(VLOOKUP($B62,main!$C$2:$R$62,14,FALSE)=0,"",VLOOKUP($B62,main!$C$2:$R$62,14,FALSE))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G62" s="35">
         <f>+IF(VLOOKUP($B62,main!$C$2:$R$62,15,FALSE)=0,"",VLOOKUP($B62,main!$C$2:$R$62,15,FALSE))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H62" s="35" t="str">
         <f>+IF(VLOOKUP($B62,main!$C$2:$R$62,16,FALSE)=0,"",VLOOKUP($B62,main!$C$2:$R$62,16,FALSE))</f>
